--- a/public/conversion.xlsx
+++ b/public/conversion.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="12860"/>
+    <workbookView windowWidth="21140" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
   <si>
     <t>raw_unit</t>
   </si>
@@ -57,6 +57,36 @@
   </si>
   <si>
     <t>万吨</t>
+  </si>
+  <si>
+    <t>立方米</t>
+  </si>
+  <si>
+    <t>万立方米</t>
+  </si>
+  <si>
+    <t>千瓦时</t>
+  </si>
+  <si>
+    <t>亿千瓦时</t>
+  </si>
+  <si>
+    <t>万</t>
+  </si>
+  <si>
+    <t>百万吨</t>
+  </si>
+  <si>
+    <t>兆瓦时</t>
+  </si>
+  <si>
+    <t>吉焦</t>
+  </si>
+  <si>
+    <t>MWh</t>
+  </si>
+  <si>
+    <t>GJ</t>
   </si>
 </sst>
 </file>
@@ -670,8 +700,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1018,7 +1049,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.5384615384615" customWidth="1"/>
@@ -1066,7 +1097,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>1e-9</v>
+        <v>1e-8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1077,7 +1108,7 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>1e-9</v>
+        <v>1e-8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1099,7 +1130,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1144,6 +1175,116 @@
       </c>
       <c r="C11">
         <v>10000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>1e-8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>1e-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21">
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
